--- a/AI Audit Log_HoHuynhMinhHuy.xlsx
+++ b/AI Audit Log_HoHuynhMinhHuy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kỳ 7 Sum26\SWD392\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kỳ 7 Sum26\SWD392\AI Audit Log_De190246\ai-audit-log-MinhHuy1303\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -90,6 +90,90 @@
   </si>
   <si>
     <t>Phản hồi: AI giải thích Actor là đối tượng tương tác với hệ thống, còn UseCase là chức năng hệ thống cung cấp. AI đưa ví dụ hệ thống ATM với Actor là Khách hàng và UseCase là Rút tiền. Quyết định: Tôi giữ lại ví dụ ATM vì dễ hiểu và bổ sung thêm Actor phụ như Ngân hàng để hoàn thiện sơ đồ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Database Design</t>
+  </si>
+  <si>
+    <t>“Thiết kế database cho hệ thống học tiếng Anh gồm User, Course, Lesson và Quiz.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các bảng, khóa chính/khóa ngoại và quan hệ giữa các bảng. Quyết định: Tôi bổ sung thêm bảng Result để lưu kết quả làm bài của học viên.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất mã hóa password bằng bcrypt, JWT authentication và validation dữ liệu đầu vào. Quyết định: Tôi bổ sung rate limiting và CORS để hạn chế tấn công brute force và truy cập trái phép.</t>
+  </si>
+  <si>
+    <t>UI/UX Design</t>
+  </si>
+  <si>
+    <t>“Đề xuất cải thiện trải nghiệm người dùng cho ứng dụng học tiếng Anh.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất dark mode, animation nhẹ và thông báo tiến độ học tập. Quyết định: Tôi chọn thêm progress bar và streak learning để tăng động lực học tập cho người dùng.</t>
+  </si>
+  <si>
+    <t>Component Diagram</t>
+  </si>
+  <si>
+    <t>“Thiết kế Component Diagram cho hệ thống React Native + Node.js + MongoDB.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chia hệ thống thành Mobile App, REST API Server và Database Layer. Quyết định: Tôi thêm Authentication Service để tách riêng chức năng xác thực người dùng.</t>
+  </si>
+  <si>
+    <t>Architectural Pattern</t>
+  </si>
+  <si>
+    <t>“So sánh MVC và MVP trong thiết kế phần mềm.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích cách Controller và Presenter xử lý dữ liệu trong từng mô hình. Quyết định: Tôi chọn MVC vì phù hợp với ExpressJS và React Native đang sử dụng.</t>
+  </si>
+  <si>
+    <t>UML Diagram</t>
+  </si>
+  <si>
+    <t>“Thiết kế Activity Diagram cho chức năng đăng nhập.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI mô tả các bước nhập tài khoản, xác thực dữ liệu và chuyển hướng người dùng. Quyết định: Tôi thêm bước kiểm tra tài khoản bị khóa sau nhiều lần đăng nhập sai.</t>
+  </si>
+  <si>
+    <t>Software Architecture</t>
+  </si>
+  <si>
+    <t>“Giải thích sự khác nhau giữa Layered Architecture và Client-Server Architecture.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI so sánh cấu trúc phân tầng và mô hình client-server về cách tổ chức hệ thống và giao tiếp dữ liệu. Quyết định: Tôi chọn Layered Architecture cho dự án vì dễ bảo trì và phân tách trách nhiệm rõ ràng.</t>
+  </si>
+  <si>
+    <t>MongoDB</t>
+  </si>
+  <si>
+    <t>“So sánh MongoDB và MySQL trong phát triển web application.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích MongoDB là NoSQL lưu dữ liệu dạng document, còn MySQL là relational database dùng bảng và quan hệ. Quyết định: Tôi chọn MongoDB vì dữ liệu của dự án linh hoạt và dễ mở rộng schema.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mongoose Schema</t>
+  </si>
+  <si>
+    <t>“Thiết kế Mongoose Schema cho User gồm username, email và password.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất tạo UserSchema với required, unique và validation cho email. Quyết định: Tôi bổ sung thêm role và avatar để hỗ trợ phân quyền và hồ sơ người dùng.</t>
+  </si>
+  <si>
+    <t>Connection Management</t>
+  </si>
+  <si>
+    <t>“Cách kết nối MongoDB Atlas bằng Mongoose.”</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn dùng mongoose.connect() với connection string từ MongoDB Atlas. Quyết định: Tôi lưu URI trong file .env để tăng tính bảo mật.</t>
   </si>
 </sst>
 </file>
@@ -590,18 +674,214 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="41.4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="41.4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="41.4">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="55.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="55.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="41.4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="41.4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/AI Audit Log_HoHuynhMinhHuy.xlsx
+++ b/AI Audit Log_HoHuynhMinhHuy.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="2"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -174,6 +174,111 @@
   </si>
   <si>
     <t>Phản hồi: AI hướng dẫn dùng mongoose.connect() với connection string từ MongoDB Atlas. Quyết định: Tôi lưu URI trong file .env để tăng tính bảo mật.</t>
+  </si>
+  <si>
+    <t>Database Design</t>
+  </si>
+  <si>
+    <t>"Thiết kế cơ sở dữ liệu cho hệ thống quản lý bãi đỗ xe gồm User, ParkingSlot, ParkingSession và Payment."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các bảng, khóa chính, khóa ngoại và quan hệ giữa các thực thể. Quyết định: Tôi bổ sung thêm trường checkOutTime, status và bảng Payment để quản lý lịch sử thanh toán và trạng thái phiên gửi xe.</t>
+  </si>
+  <si>
+    <t>"Đề xuất các biện pháp bảo mật cho hệ thống NodeJS sử dụng JWT Authentication."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất mã hóa mật khẩu bằng bcrypt, sử dụng JWT, middleware xác thực và validation dữ liệu đầu vào. Quyết định: Tôi bổ sung thêm CORS, Helmet và Rate Limiting để tăng cường bảo mật API.</t>
+  </si>
+  <si>
+    <t>Backend API Design</t>
+  </si>
+  <si>
+    <t>"Thiết kế RESTful API cho hệ thống quản lý lịch hẹn bác sĩ bằng ExpressJS và MongoDB."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các endpoint CRUD, cấu trúc Controller-Service-Model và cách sử dụng HTTP Status Code. Quyết định: Tôi áp dụng mô hình MVC và thêm chức năng populate dữ liệu bác sĩ trong danh sách lịch hẹn.</t>
+  </si>
+  <si>
+    <t>Database Optimization</t>
+  </si>
+  <si>
+    <t>"Kiểm tra và tối ưu schema MongoDB cho Parking Session."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất sử dụng ObjectId, tạo index cho các trường tìm kiếm thường xuyên và chuẩn hóa dữ liệu. Quyết định: Tôi tạo index cho slotId, licensePlate và status để tăng tốc độ truy vấn.</t>
+  </si>
+  <si>
+    <t>Frontend UI/UX Design</t>
+  </si>
+  <si>
+    <t>"Đề xuất giao diện hiện đại cho ứng dụng Todo List React Native."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý sử dụng card layout, gradient background, thống kê công việc và hiệu ứng animation. Quyết định: Tôi thiết kế lại giao diện theo phong cách mobile app hiện đại, bổ sung progress bar và task filtering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Project Architecture</t>
+  </si>
+  <si>
+    <t>"Đề xuất cấu trúc thư mục cho dự án React Native Todo App."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất tách thành các thư mục screens, components, navigation, services và hooks. Quyết định: Tôi áp dụng kiến trúc này để dễ bảo trì và mở rộng chức năng trong tương lai.</t>
+  </si>
+  <si>
+    <t>English Learning System (ELS)</t>
+  </si>
+  <si>
+    <t>"Thiết kế cơ sở dữ liệu cho hệ thống học tiếng Anh gồm User, Course, Lesson, Quiz và Result."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất các bảng và quan hệ dữ liệu giữa khóa học, bài học và bài kiểm tra. Quyết định: Tôi bổ sung bảng Result để lưu điểm và lịch sử làm bài của học viên.</t>
+  </si>
+  <si>
+    <t>Documentation (SRS)</t>
+  </si>
+  <si>
+    <t>"Viết tài liệu Software Requirements Specification cho hệ thống học tiếng Anh."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hỗ trợ xây dựng phần Introduction, Functional Requirements và Non-functional Requirements. Quyết định: Tôi chỉnh sửa nội dung theo phạm vi dự án và chuẩn hóa tài liệu theo mẫu của môn SDN302.</t>
+  </si>
+  <si>
+    <t>Business Logic</t>
+  </si>
+  <si>
+    <t>"Kiểm tra logic cập nhật trạng thái Parking Slot khi xe check-in và check-out."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất cập nhật trạng thái occupied khi tạo phiên gửi xe và available khi kết thúc phiên. Quyết định: Tôi triển khai tự động cập nhật trạng thái slot trong controller để đảm bảo tính nhất quán dữ liệu.</t>
+  </si>
+  <si>
+    <t>Testing &amp; Debugging</t>
+  </si>
+  <si>
+    <t>"Kiểm tra lỗi trong Appointment Controller sử dụng async/await."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích cơ chế hoạt động của async/await, xử lý exception bằng try-catch và trả về response phù hợp. Quyết định: Tôi bổ sung xử lý lỗi tập trung và kiểm tra ObjectId trước khi truy vấn MongoDB.</t>
+  </si>
+  <si>
+    <t>Presentation &amp; Business Model</t>
+  </si>
+  <si>
+    <t>"Đề xuất mô hình kinh doanh cho ứng dụng hỗ trợ học lái xe."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Freemium Model, B2C cho người học và B2B SaaS cho trung tâm đào tạo lái xe. Quyết định: Tôi xây dựng phần Business Model gồm hai nhóm khách hàng riêng biệt và bổ sung Market Fit cho từng nhóm.</t>
+  </si>
+  <si>
+    <t>AI-assisted Development</t>
+  </si>
+  <si>
+    <t>"Đề xuất các tính năng sáng tạo giúp ứng dụng nổi bật hơn."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý Parallax Effect, Smart Reminder, Daily Streak và thống kê tiến độ học tập. Quyết định: Tôi lựa chọn các tính năng có thể triển khai trong thời gian dự án để tăng tính sáng tạo và trải nghiệm người dùng.</t>
   </si>
 </sst>
 </file>
@@ -817,7 +922,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20.8984375" customWidth="1"/>
@@ -869,17 +974,75 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4"/>
+    <row r="4" spans="1:5" ht="55.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="55.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="55.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -888,9 +1051,129 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="55.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="55.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="55.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI Audit Log_HoHuynhMinhHuy.xlsx
+++ b/AI Audit Log_HoHuynhMinhHuy.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="3"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -279,6 +280,51 @@
   </si>
   <si>
     <t>Phản hồi: AI gợi ý Parallax Effect, Smart Reminder, Daily Streak và thống kê tiến độ học tập. Quyết định: Tôi lựa chọn các tính năng có thể triển khai trong thời gian dự án để tăng tính sáng tạo và trải nghiệm người dùng.</t>
+  </si>
+  <si>
+    <t>ERD &amp; Relationship Design</t>
+  </si>
+  <si>
+    <t>"Kiểm tra sơ đồ ERD và đề xuất các mối quan hệ giữa các bảng trong hệ thống."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích các quan hệ 1-1, 1-N và N-N giữa các thực thể, đồng thời đề xuất sử dụng khóa ngoại phù hợp. Quyết định: Tôi điều chỉnh lại một số quan hệ và bổ sung ràng buộc dữ liệu để tránh dữ liệu trùng lặp.</t>
+  </si>
+  <si>
+    <t>API Documentation</t>
+  </si>
+  <si>
+    <t>"Tạo tài liệu mô tả các API cho hệ thống quản lý bãi đỗ xe."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất định dạng tài liệu gồm endpoint, method, request body, response và mã lỗi. Quyết định: Tôi áp dụng cấu trúc này để xây dựng tài liệu API dễ hiểu cho người dùng và giảng viên.</t>
+  </si>
+  <si>
+    <t>User Interface Improvement</t>
+  </si>
+  <si>
+    <t>"Đề xuất cách cải thiện giao diện để ứng dụng trông chuyên nghiệp hơn."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI gợi ý sử dụng màu sắc đồng nhất, card layout, icon và khoảng trắng hợp lý. Quyết định: Tôi chỉnh sửa giao diện theo phong cách hiện đại, giúp trải nghiệm người dùng trực quan hơn.</t>
+  </si>
+  <si>
+    <t>Code Review &amp; Refactoring</t>
+  </si>
+  <si>
+    <t>"Đánh giá chất lượng source code và đề xuất cải tiến."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phát hiện các đoạn code lặp lại và đề xuất tách thành các hàm hoặc component tái sử dụng. Quyết định: Tôi refactor một số module để tăng tính dễ bảo trì và mở rộng.</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>"Đề xuất cách xử lý lỗi cho hệ thống ExpressJS và MongoDB."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất sử dụng middleware xử lý lỗi tập trung và chuẩn hóa thông báo lỗi trả về client. Quyết định: Tôi xây dựng middleware riêng để quản lý lỗi và giảm trùng lặp code trong controller.</t>
   </si>
 </sst>
 </file>
@@ -1176,4 +1222,119 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="55.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="41.4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_HoHuynhMinhHuy.xlsx
+++ b/AI Audit Log_HoHuynhMinhHuy.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="4"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -325,6 +326,78 @@
   </si>
   <si>
     <t>Phản hồi: AI đề xuất sử dụng middleware xử lý lỗi tập trung và chuẩn hóa thông báo lỗi trả về client. Quyết định: Tôi xây dựng middleware riêng để quản lý lỗi và giảm trùng lặp code trong controller.</t>
+  </si>
+  <si>
+    <t>MongoDB Schema Design</t>
+  </si>
+  <si>
+    <t>"Thiết kế schema MongoDB cho hệ thống quản lý lịch hẹn bác sĩ gồm Doctor, Appointment và Patient."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất sử dụng ObjectId để liên kết dữ liệu và thiết kế các collection theo hướng chuẩn hóa. Quyết định: Tôi áp dụng mô hình tham chiếu dữ liệu bằng ObjectId và sử dụng populate để hiển thị thông tin liên quan.</t>
+  </si>
+  <si>
+    <t>Controller Development</t>
+  </si>
+  <si>
+    <t>"Giải thích chi tiết Appointment Controller sử dụng async/await trong NodeJS."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích luồng xử lý request, cách hoạt động của async/await và xử lý lỗi bằng try-catch. Quyết định: Tôi hiểu rõ hơn về bất đồng bộ trong JavaScript và cải thiện khả năng giải thích source code khi bảo vệ đồ án.</t>
+  </si>
+  <si>
+    <t>Business Logic Validation</t>
+  </si>
+  <si>
+    <t>"Kiểm tra logic tránh tạo nhiều phiên gửi xe cùng lúc cho một bãi đỗ."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất kiểm tra trạng thái slot trước khi tạo Parking Session mới và cập nhật trạng thái khi kết thúc phiên gửi xe. Quyết định: Tôi bổ sung điều kiện kiểm tra dữ liệu để tránh phát sinh dữ liệu không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Prompt Engineering</t>
+  </si>
+  <si>
+    <t>"Viết prompt chi tiết để AI tạo ứng dụng Todo List bằng React Native theo mô hình component."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xây dựng prompt mô tả đầy đủ cấu trúc thư mục, chức năng và giao diện. Quyết định: Tôi sử dụng prompt này để tăng hiệu quả hỗ trợ lập trình từ AI và tiết kiệm thời gian phát triển.</t>
+  </si>
+  <si>
+    <t>UI/UX Review</t>
+  </si>
+  <si>
+    <t>"Đánh giá giao diện hiện tại và đề xuất cải tiến để ứng dụng trông chuyên nghiệp hơn."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI chỉ ra các vấn đề về khoảng cách, màu sắc và bố cục, đồng thời đề xuất thiết kế hiện đại hơn. Quyết định: Tôi chỉnh sửa giao diện theo hướng tối giản và đồng nhất trải nghiệm người dùng.</t>
+  </si>
+  <si>
+    <t>Learning Support</t>
+  </si>
+  <si>
+    <t>"Giải thích chi tiết kiểm định Welch's t-test và ý nghĩa các công thức thống kê."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích từng bước suy luận, công thức và điều kiện áp dụng của phép kiểm định. Quyết định: Tôi sử dụng phần giải thích này để hiểu bản chất bài học thay vì chỉ ghi nhớ công thức.</t>
+  </si>
+  <si>
+    <t>Cloud Deployment</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn deploy ứng dụng NodeJS lên Heroku và kết nối MongoDB Atlas."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn cấu hình biến môi trường, Procfile, build script và cách whitelist IP trên MongoDB Atlas. Quyết định: Tôi thực hiện deploy thành công ứng dụng lên môi trường cloud và hiểu rõ quy trình triển khai thực tế.</t>
+  </si>
+  <si>
+    <t>REST API Development</t>
+  </si>
+  <si>
+    <t>"Xây dựng chức năng Create Booking với Mongoose và kiểm tra số lượng ghế còn trống."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn validate dữ liệu đầu vào, cập nhật số ghế còn lại và sử dụng populate để lấy thông tin liên quan. Quyết định: Tôi áp dụng giải pháp vào bài thực hành SDN302 và hoàn thiện API đặt vé.</t>
   </si>
 </sst>
 </file>
@@ -1337,4 +1410,147 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="55.2">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="55.2">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="55.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="55.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="55.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_HoHuynhMinhHuy.xlsx
+++ b/AI Audit Log_HoHuynhMinhHuy.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="5"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week5" sheetId="5" r:id="rId5"/>
     <sheet name="Week6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week7" sheetId="7" r:id="rId7"/>
+    <sheet name="Week8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="158">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -398,6 +400,126 @@
   </si>
   <si>
     <t>Phản hồi: AI hướng dẫn validate dữ liệu đầu vào, cập nhật số ghế còn lại và sử dụng populate để lấy thông tin liên quan. Quyết định: Tôi áp dụng giải pháp vào bài thực hành SDN302 và hoàn thiện API đặt vé.</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn xây dựng REST API CRUD bằng Express.js và Mongoose cho hệ thống quản lý."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn xây dựng Controller, Route, Model, validate dữ liệu và xử lý lỗi. Quyết định: Tôi áp dụng kiến trúc MVC cho toàn bộ backend.</t>
+  </si>
+  <si>
+    <t>"Thiết kế schema MongoDB cho hệ thống học tiếng Anh gồm User, Course, Lesson, Question, Result và Progress."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất chuẩn hóa schema bằng ObjectId, sử dụng reference giữa các collection và populate để lấy dữ liệu liên quan. Quyết định: Tôi áp dụng mô hình tham chiếu thay vì nhúng dữ liệu để dễ mở rộng và bảo trì.</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Security</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn đăng nhập bằng JWT, bcrypt và phân quyền Admin/User."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích quy trình mã hóa mật khẩu, tạo JWT và middleware xác thực. Quyết định: Tôi tích hợp JWT Authentication và Role-based Authorization cho dự án.</t>
+  </si>
+  <si>
+    <t>"Kiểm tra logic khi tạo lịch hẹn/đăng ký để tránh dữ liệu trùng hoặc không hợp lệ."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất kiểm tra trạng thái dữ liệu trước khi tạo mới và validate các điều kiện nghiệp vụ. Quyết định: Tôi bổ sung các điều kiện kiểm tra nhằm đảm bảo tính toàn vẹn dữ liệu.</t>
+  </si>
+  <si>
+    <t>Cloud Storage Integration</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn cấu hình Cloudinary để upload và quản lý hình ảnh."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn tạo Cloudinary Account, cấu hình biến môi trường và upload bằng Multer + Cloudinary SDK. Quyết định: Tôi chuyển việc lưu ảnh từ local sang Cloudinary để thuận tiện triển khai.</t>
+  </si>
+  <si>
+    <t>HTTPS Configuration</t>
+  </si>
+  <si>
+    <t>"Chuyển dự án Express từ HTTP sang HTTPS bằng OpenSSL với server.key và server.crt."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn tạo chứng chỉ SSL, cấu hình HTTPS Server và đọc certificate bằng Node.js. Quyết định: Tôi cấu hình HTTPS cho server nhằm đáp ứng yêu cầu bảo mật của dự án.</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn deploy ứng dụng Node.js lên môi trường Cloud và kết nối MongoDB Atlas."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn cấu hình biến môi trường, MongoDB Atlas, whitelist IP và build project. Quyết định: Tôi triển khai dự án lên môi trường cloud để kiểm thử thực tế.</t>
+  </si>
+  <si>
+    <t>OCR &amp; Data Extraction</t>
+  </si>
+  <si>
+    <t>"OCR toàn bộ hình ảnh trong file Word để chuyển thành dữ liệu Reading, Listening."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn trích xuất văn bản từ hình ảnh và chuyển thành dữ liệu có cấu trúc. Quyết định: Tôi sử dụng dữ liệu OCR để xây dựng ngân hàng câu hỏi cho hệ thống học tiếng Anh.</t>
+  </si>
+  <si>
+    <t>"Đánh giá giao diện ứng dụng và đề xuất cải tiến theo hướng hiện đại."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI góp ý về màu sắc, khoảng cách, bố cục và trải nghiệm người dùng. Quyết định: Tôi chỉnh sửa giao diện theo phong cách tối giản và đồng nhất.</t>
+  </si>
+  <si>
+    <t>Figma Design</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn chỉnh sửa biển báo giao thông, tách nền và thiết kế icon trong Figma."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn sử dụng Pen Tool, Boolean, Remove Background và đặt tên asset. Quyết định: Tôi chuẩn hóa bộ hình ảnh trước khi đưa vào Unity và React Native.</t>
+  </si>
+  <si>
+    <t>Git Collaboration</t>
+  </si>
+  <si>
+    <t>"Bị lỗi gì khi git push bị rejected (fetch first)?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI giải thích remote đã có commit mới và hướng dẫn git pull --rebase hoặc merge trước khi push. Quyết định: Tôi đồng bộ branch với GitHub trước khi push để tránh xung đột.</t>
+  </si>
+  <si>
+    <t>Express &amp; EJS Setup</t>
+  </si>
+  <si>
+    <t>"Lỗi Cannot find module 'ejs' là gì?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn cài đặt ejs, cấu hình view engine và thư mục views. Quyết định: Tôi cấu hình thành công ứng dụng Express sử dụng EJS.</t>
+  </si>
+  <si>
+    <t>React Native Setup</t>
+  </si>
+  <si>
+    <t>"Expo không được nhận diện, chạy ứng dụng React Native như thế nào?"</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI hướng dẫn cài đặt Expo CLI, chạy npx expo start và xử lý lỗi emulator Android. Quyết định: Tôi cấu hình môi trường React Native đúng cách để tiếp tục phát triển ứng dụng.</t>
+  </si>
+  <si>
+    <t>Presentation Support</t>
+  </si>
+  <si>
+    <t>"Dịch câu mở đầu thuyết trình checkpoint 3 của dự án Driving Test Simulator sang tiếng Anh."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cung cấp bản dịch tự nhiên, phù hợp với ngữ cảnh thuyết trình học thuật. Quyết định: Tôi sử dụng bản dịch này khi chuẩn bị slide và thuyết trình.</t>
+  </si>
+  <si>
+    <t>Database Modeling</t>
+  </si>
+  <si>
+    <t>"Kiểm tra sơ đồ ERD có đúng chuẩn Chen hay chưa."</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích Entity, Relationship, Attribute và Cardinality, chỉ ra các điểm chưa đúng chuẩn. Quyết định: Tôi chỉnh sửa ERD theo đúng ký pháp Chen trước khi đưa vào báo cáo.</t>
   </si>
 </sst>
 </file>
@@ -1553,4 +1675,276 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="69">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="41.4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="55.2">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="55.2">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="41.4">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="20.8984375" customWidth="1"/>
+    <col min="2" max="2" width="26.8984375" customWidth="1"/>
+    <col min="3" max="3" width="25.19921875" customWidth="1"/>
+    <col min="4" max="4" width="52.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="55.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="41.4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="41.4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="41.4">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="41.4">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="55.2">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="55.2">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="55.2">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>